--- a/artfynd/A 27865-2024 artfynd.xlsx
+++ b/artfynd/A 27865-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78579404</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769966</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120690433</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16781511</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047911</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111191836</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769982</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16781503</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2235298</t>
         </is>
       </c>
     </row>
@@ -1975,6 +2035,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769976</t>
         </is>
       </c>
     </row>
@@ -2088,6 +2153,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047868</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2199,6 +2269,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78579409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2301,6 +2376,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96257375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2402,6 +2482,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6855547</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2513,6 +2598,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769978</t>
         </is>
       </c>
     </row>
@@ -2626,6 +2716,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2737,6 +2832,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79040433</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2851,6 +2951,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86301348</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2965,6 +3070,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101187567</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3076,6 +3186,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78579416</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3187,6 +3302,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047878</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3298,6 +3418,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2756020</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3408,6 +3533,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6855543</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3507,6 +3637,11 @@
       <c r="AY27" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6855545</t>
         </is>
       </c>
     </row>
@@ -3620,6 +3755,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78579413</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3731,6 +3871,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79215871</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3852,6 +3997,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769955</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3974,6 +4124,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769973</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4086,6 +4241,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72060385</t>
         </is>
       </c>
     </row>
@@ -4194,6 +4354,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78515259</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4305,6 +4470,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78579400</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4416,6 +4586,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78579418</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4530,6 +4705,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111392992</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4639,6 +4819,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16781514</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4748,6 +4933,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16769983</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4857,6 +5047,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16781504</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4963,6 +5158,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72034256</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5082,6 +5282,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047897</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5201,6 +5406,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047921</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5313,6 +5523,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117904086</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5420,8 +5635,58 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72047392</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>